--- a/assets/files/UAT_and_Release_Workbook.xlsx
+++ b/assets/files/UAT_and_Release_Workbook.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Overview" sheetId="1" r:id="Rc8095aa5ccc34d0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Test_Strategy" sheetId="2" r:id="Re9918b9453be4dc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Config_Validation" sheetId="3" r:id="R0d8f5851d7b641d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Interface_Validation" sheetId="4" r:id="Rde9a34240f1e4c70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_RTM" sheetId="5" r:id="Rfde8923f3a134c49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_UAT_Cases" sheetId="6" r:id="R9ce14837c2834d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_UAT_Summary" sheetId="7" r:id="R52e3927cff6a4a34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Defects" sheetId="8" r:id="R2dee0f66b4bd44e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Retest_Regression" sheetId="9" r:id="Rac58b04b822a4647"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Accepted_Exception" sheetId="10" r:id="R50bd6b0b5fe346a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Release_Baseline" sheetId="11" r:id="R6bff7a65024c49de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Gate_Evidence" sheetId="12" r:id="R993556f2d9154757"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Limitations" sheetId="13" r:id="R5b6cf48fafb24fcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Package_Gate" sheetId="14" r:id="R2f9e0e154918427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Lists" sheetId="15" r:id="R93b9e9efc9074a09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Overview" sheetId="1" r:id="Rfcf5366096864b90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Test_Strategy" sheetId="2" r:id="R6d64669e81414fce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Config_Validation" sheetId="3" r:id="Rf6ca1ce4138746e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Interface_Validation" sheetId="4" r:id="R8bc80834a1904e63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_RTM" sheetId="5" r:id="R0cbe349beabf48a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_UAT_Cases" sheetId="6" r:id="Ra7106d3365c44d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_UAT_Summary" sheetId="7" r:id="Rb9802ac59e8b4d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Defects" sheetId="8" r:id="R1434d8bd49ec4a77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Retest_Regression" sheetId="9" r:id="Rff77aeec710341b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Accepted_Exception" sheetId="10" r:id="R5c83213530fb4741"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Release_Baseline" sheetId="11" r:id="R5f1c86a30485474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Gate_Evidence" sheetId="12" r:id="Rd2f869128678453d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Limitations" sheetId="13" r:id="R20f4fe74814f4ff9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Package_Gate" sheetId="14" r:id="R30ee8c755f1b4d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Lists" sheetId="15" r:id="R2b360936e0cd4347"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -756,7 +756,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc190dff669d7401c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6842e313d02944cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -894,7 +894,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf23c366c8efe4e66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6498935b61d84f90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -948,7 +948,7 @@
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B7" s="16" t="str">
-        <x:v>UAT-APPROVED RELEASE CANDIDATE — TRAINING / CUTOVER PLANNING AUTHORIZED</x:v>
+        <x:v>UAT-APPROVED RELEASE CANDIDATE - TRAINING / CUTOVER PLANNING AUTHORIZED</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1054,7 +1054,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f6974486b14b98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5830b7a7631143bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1197,7 +1197,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fe6730102ed4bc8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3c29f719d0642b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1359,7 +1359,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc81d197c66fe4f14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7549dee550cd4323"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1523,7 +1523,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9f9c0652bcb4ea8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R605f2f4c81ae4147"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1852,7 +1852,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf14dd77f5a8494b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01bd00faf0014c0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2785,7 +2785,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra82dfe8d88e4411d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R849eb16062b248c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3069,7 +3069,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc3bad7df2254ceb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3b04efb27184e3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4641,7 +4641,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ba631f3fa2c4a63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf961736253554052"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6926,7 +6926,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda4bba2da6fc45b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b82f87c016044ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7041,7 +7041,7 @@
     </x:row>
     <x:row r="9" ht="38" customHeight="1">
       <x:c r="A9" s="27" t="str">
-        <x:v>GATE PRINCIPLE: GL-002/003 — overall &gt;=90% cannot conceal an unresolved business-critical/Must-Have failure; every failed result must link to defect, decision, accepted exception, or process correction.</x:v>
+        <x:v>GATE PRINCIPLE: GL-002/003 - overall &gt;=90% cannot conceal an unresolved business-critical/Must-Have failure; every failed result must link to defect, decision, accepted exception, or process correction.</x:v>
       </x:c>
       <x:c r="B9" s="27"/>
       <x:c r="C9" s="27"/>
@@ -7459,7 +7459,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d9f7f8abc06435a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R564b85ddb2f94a85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7763,7 +7763,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd12717629d204c5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7c8803333e04ec9"/>
   </x:tableParts>
 </x:worksheet>
 </file>